--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129021795</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129021752</v>
+        <v>129021795</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462455</v>
+        <v>462584</v>
       </c>
       <c r="R2" t="n">
-        <v>6702949</v>
+        <v>6702829</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,17 +760,13 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Cirka 6 meter ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,46 +785,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129021795</v>
+        <v>129021752</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462584</v>
+        <v>462455</v>
       </c>
       <c r="R3" t="n">
-        <v>6702829</v>
+        <v>6702949</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,13 +866,17 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Cirka 6 meter ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,7 +898,7 @@
         <v>129021758</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -675,46 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129021795</v>
+        <v>129021752</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462584</v>
+        <v>462455</v>
       </c>
       <c r="R2" t="n">
-        <v>6702829</v>
+        <v>6702949</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,13 +756,17 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Cirka 6 meter ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,42 +785,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129021752</v>
+        <v>129021795</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462455</v>
+        <v>462584</v>
       </c>
       <c r="R3" t="n">
-        <v>6702949</v>
+        <v>6702829</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,17 +870,13 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Cirka 6 meter ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129021752</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129021795</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129021758</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129021795</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129021752</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129021795</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129021758</v>
       </c>
       <c r="B4" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129021795</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129021795</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129021752</v>
+        <v>129021795</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462455</v>
+        <v>462584</v>
       </c>
       <c r="R2" t="n">
-        <v>6702949</v>
+        <v>6702829</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,17 +760,13 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Cirka 6 meter ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,46 +785,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129021795</v>
+        <v>129021752</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462584</v>
+        <v>462455</v>
       </c>
       <c r="R3" t="n">
-        <v>6702829</v>
+        <v>6702949</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,13 +866,17 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Cirka 6 meter ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -675,46 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129021795</v>
+        <v>129021752</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462584</v>
+        <v>462455</v>
       </c>
       <c r="R2" t="n">
-        <v>6702829</v>
+        <v>6702949</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,13 +756,17 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Cirka 6 meter ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,42 +785,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129021752</v>
+        <v>129021795</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462455</v>
+        <v>462584</v>
       </c>
       <c r="R3" t="n">
-        <v>6702949</v>
+        <v>6702829</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,17 +870,13 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Cirka 6 meter ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,7 +898,7 @@
         <v>129021758</v>
       </c>
       <c r="B4" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129021752</v>
+        <v>129021795</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462455</v>
+        <v>462584</v>
       </c>
       <c r="R2" t="n">
-        <v>6702949</v>
+        <v>6702829</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,17 +760,13 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Cirka 6 meter ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,46 +785,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129021795</v>
+        <v>129021752</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462584</v>
+        <v>462455</v>
       </c>
       <c r="R3" t="n">
-        <v>6702829</v>
+        <v>6702949</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,13 +866,17 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Cirka 6 meter ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,7 +898,7 @@
         <v>129021758</v>
       </c>
       <c r="B4" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129021795</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -675,46 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129021795</v>
+        <v>129021752</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462584</v>
+        <v>462455</v>
       </c>
       <c r="R2" t="n">
-        <v>6702829</v>
+        <v>6702949</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,13 +756,17 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Cirka 6 meter ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,42 +785,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129021752</v>
+        <v>129021795</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462455</v>
+        <v>462584</v>
       </c>
       <c r="R3" t="n">
-        <v>6702949</v>
+        <v>6702829</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,17 +870,13 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Cirka 6 meter ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129021795</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129021805</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129021799</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129021752</v>
+        <v>129021795</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462455</v>
+        <v>462584</v>
       </c>
       <c r="R2" t="n">
-        <v>6702949</v>
+        <v>6702829</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,17 +760,13 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Cirka 6 meter ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,46 +785,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129021795</v>
+        <v>129021752</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462584</v>
+        <v>462455</v>
       </c>
       <c r="R3" t="n">
-        <v>6702829</v>
+        <v>6702949</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,13 +866,17 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Cirka 6 meter ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -675,46 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129021795</v>
+        <v>129021758</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462584</v>
+        <v>462463</v>
       </c>
       <c r="R2" t="n">
-        <v>6702829</v>
+        <v>6702948</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -788,7 +779,7 @@
         <v>129021752</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,37 +886,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129021758</v>
+        <v>129021795</v>
       </c>
       <c r="B4" t="n">
-        <v>78801</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462463</v>
+        <v>462584</v>
       </c>
       <c r="R4" t="n">
-        <v>6702948</v>
+        <v>6702829</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129021805</v>
+        <v>129021799</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462577</v>
+        <v>462586</v>
       </c>
       <c r="R5" t="n">
-        <v>6702844</v>
+        <v>6702820</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129021799</v>
+        <v>129021805</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462586</v>
+        <v>462577</v>
       </c>
       <c r="R6" t="n">
-        <v>6702820</v>
+        <v>6702844</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021752</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021795</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021799</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,8 +1238,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021805</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129021752</v>
+        <v>135616394</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>79168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,31 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462455</v>
+        <v>462444</v>
       </c>
       <c r="R3" t="n">
-        <v>6702949</v>
+        <v>6702915</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,17 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Cirka 6 meter ringhack på tall.</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,52 +886,43 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129021752</t>
+          <t>https://artportalen.se/Sighting/135616394</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129021795</v>
+        <v>135616410</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>79168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462584</v>
+        <v>462490</v>
       </c>
       <c r="R4" t="n">
-        <v>6702829</v>
+        <v>6702849</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,12 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,52 +992,43 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129021795</t>
+          <t>https://artportalen.se/Sighting/135616410</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129021799</v>
+        <v>135616414</v>
       </c>
       <c r="B5" t="n">
-        <v>99118</v>
+        <v>79168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462586</v>
+        <v>462505</v>
       </c>
       <c r="R5" t="n">
-        <v>6702820</v>
+        <v>6702840</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,12 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,52 +1098,43 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129021799</t>
+          <t>https://artportalen.se/Sighting/135616414</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129021805</v>
+        <v>135616422</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>79168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462577</v>
+        <v>462522</v>
       </c>
       <c r="R6" t="n">
-        <v>6702844</v>
+        <v>6702817</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,12 +1172,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1204,1344 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135616422</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135616434</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79168</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>462507</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6702820</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616434</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129021752</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>462455</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6702949</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Cirka 6 meter ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021752</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135616452</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>462557</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6702785</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616452</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135616405</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>462454</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6702861</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616405</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135616443</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>462526</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6702805</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616443</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135616485</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>462573</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6702789</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616485</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135616495</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>462573</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6702781</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616495</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129021795</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>462584</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6702829</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021795</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129021799</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>462586</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6702820</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021799</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129021805</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>462577</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6702844</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129021805</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135616362</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>462349</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6702802</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616362</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135616427</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>462490</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6702834</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616427</t>
         </is>
       </c>
     </row>
@@ -1251,6 +2552,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135616394</v>
       </c>
       <c r="B3" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135616410</v>
       </c>
       <c r="B4" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135616414</v>
       </c>
       <c r="B5" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135616422</v>
       </c>
       <c r="B6" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135616434</v>
       </c>
       <c r="B7" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135616362</v>
       </c>
       <c r="B17" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>135616427</v>
       </c>
       <c r="B18" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129021752</v>
+        <v>135616394</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>79198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,31 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462455</v>
+        <v>462444</v>
       </c>
       <c r="R3" t="n">
-        <v>6702949</v>
+        <v>6702915</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,17 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Cirka 6 meter ringhack på tall.</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,52 +886,43 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129021752</t>
+          <t>https://artportalen.se/Sighting/135616394</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129021795</v>
+        <v>135616410</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>79198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462584</v>
+        <v>462490</v>
       </c>
       <c r="R4" t="n">
-        <v>6702829</v>
+        <v>6702849</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,12 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,52 +992,43 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129021795</t>
+          <t>https://artportalen.se/Sighting/135616410</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129021799</v>
+        <v>135616414</v>
       </c>
       <c r="B5" t="n">
-        <v>99118</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462586</v>
+        <v>462505</v>
       </c>
       <c r="R5" t="n">
-        <v>6702820</v>
+        <v>6702840</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,12 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,52 +1098,43 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129021799</t>
+          <t>https://artportalen.se/Sighting/135616414</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129021805</v>
+        <v>135616422</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>79198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462577</v>
+        <v>462522</v>
       </c>
       <c r="R6" t="n">
-        <v>6702844</v>
+        <v>6702817</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,12 +1172,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1204,1344 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135616422</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135616434</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>462507</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6702820</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616434</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129021752</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>462455</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6702949</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Cirka 6 meter ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021752</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135616452</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>462557</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6702785</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616452</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135616405</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>462454</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6702861</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616405</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135616443</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>462526</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6702805</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616443</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135616485</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>462573</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6702789</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616485</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135616495</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>462573</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6702781</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616495</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129021795</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>462584</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6702829</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021795</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129021799</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>462586</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6702820</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021799</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129021805</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>462577</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6702844</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129021805</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135616362</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>462349</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6702802</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616362</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135616427</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öster Stenbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>462490</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6702834</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135616427</t>
         </is>
       </c>
     </row>
@@ -1251,6 +2552,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135616394</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135616410</v>
       </c>
       <c r="B4" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135616414</v>
       </c>
       <c r="B5" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135616422</v>
       </c>
       <c r="B6" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135616434</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>135616452</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>135616405</v>
       </c>
       <c r="B10" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135616443</v>
       </c>
       <c r="B11" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>135616485</v>
       </c>
       <c r="B12" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>135616495</v>
       </c>
       <c r="B13" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135616362</v>
       </c>
       <c r="B17" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>135616427</v>
       </c>
       <c r="B18" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135616394</v>
       </c>
       <c r="B3" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135616410</v>
       </c>
       <c r="B4" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135616414</v>
       </c>
       <c r="B5" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135616422</v>
       </c>
       <c r="B6" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135616434</v>
       </c>
       <c r="B7" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135616362</v>
       </c>
       <c r="B17" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>135616427</v>
       </c>
       <c r="B18" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33005-2025 artfynd.xlsx
+++ b/artfynd/A 33005-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135616394</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135616410</v>
       </c>
       <c r="B4" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135616414</v>
       </c>
       <c r="B5" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135616422</v>
       </c>
       <c r="B6" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135616434</v>
       </c>
       <c r="B7" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>135616452</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135616362</v>
       </c>
       <c r="B17" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>135616427</v>
       </c>
       <c r="B18" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
